--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D307B6-8FF3-4EE0-8E36-C61AE2745BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2A0D3EF5B4AE71D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D48B3153-B8E7-4C86-94A4-32E8757BEF5F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 09-09-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 14-09-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2A0D3EF5B4AE71D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D48B3153-B8E7-4C86-94A4-32E8757BEF5F}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2A75E636A8C070D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D8AFBF9-ED04-48CF-9CD2-9E22B277F537}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2A75E636A8C070D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D8AFBF9-ED04-48CF-9CD2-9E22B277F537}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EA6A5C-5F64-4266-A8EB-E39CC3A95F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EA6A5C-5F64-4266-A8EB-E39CC3A95F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB051AF4-8E40-4694-A761-90657DB46EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 14-09-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 17-09-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB051AF4-8E40-4694-A761-90657DB46EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6C9163-4B11-4760-868A-4A386591DF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6C9163-4B11-4760-868A-4A386591DF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2A2FD6B2827271D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{077F93ED-06A2-4587-9C73-49428BF458D5}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 17-09-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 18-09-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2A2FD6B2827271D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{077F93ED-06A2-4587-9C73-49428BF458D5}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2A68F6F7A54070D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61544E7B-87A4-475D-9586-941FBAF2E8B7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 18-09-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 21-09-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2A68F6F7A54070D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61544E7B-87A4-475D-9586-941FBAF2E8B7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED14334B-CB4B-4F4F-9B6A-0BDFD98D0824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED14334B-CB4B-4F4F-9B6A-0BDFD98D0824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720897FA-8144-4B1A-86A3-AF920F71E584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 21-09-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 22-09-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720897FA-8144-4B1A-86A3-AF920F71E584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E046A1-6289-4040-96D7-A660883179F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E046A1-6289-4040-96D7-A660883179F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC922D3A-25FF-4FBB-AEEF-4EC8D479FD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 22-09-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 23-09-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC922D3A-25FF-4FBB-AEEF-4EC8D479FD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2A3896B4AD0471D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7101C8FF-26CD-417D-90F8-DB388E0A4462}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2A3896B4AD0471D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7101C8FF-26CD-417D-90F8-DB388E0A4462}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2ACC56F78ED870D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3985F694-D76A-43BC-A838-333D2B4FE83C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 23-09-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 24-09-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2ACC56F78ED870D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3985F694-D76A-43BC-A838-333D2B4FE83C}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2AE63EF385D470D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F6CE052-E191-4EF3-A6AE-B1B5DB4A8677}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2AE63EF385D470D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F6CE052-E191-4EF3-A6AE-B1B5DB4A8677}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFF8DD1-7BBF-4AE0-9BD8-4AFBB967C0D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 24-09-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 28-09-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFF8DD1-7BBF-4AE0-9BD8-4AFBB967C0D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2A654EF0B24C70D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B1F5705-098F-4F42-BD7D-8551487EB3E7}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 28-09-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 02-10-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E046A1-6289-4040-96D7-A660883179F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52657151-D664-4208-B12D-CDAD3EB59A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 22-09-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 07-10-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2A654EF0B24C70D888C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B1F5705-098F-4F42-BD7D-8551487EB3E7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11F6E14-49DF-47C4-BEF9-C362E5CAA586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 02-10-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 07-10-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -467,9 +467,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -556,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -611,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -637,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -651,7 +651,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -680,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -764,7 +764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -822,7 +822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -879,7 +879,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11F6E14-49DF-47C4-BEF9-C362E5CAA586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2A030E729C9271D888CD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{404BA5A5-30AE-4108-8258-3E9A41BF2ACA}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 07-10-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 08-10-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2A030E729C9271D888CD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{404BA5A5-30AE-4108-8258-3E9A41BF2ACA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B9066B-02DE-4284-9119-BB62558F3CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 08-10-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 09-10-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B9066B-02DE-4284-9119-BB62558F3CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B42BDF-F135-4A19-9538-F00DD08C7812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Fodterapisystemer_excel.XLSX
+++ b/html/Fodterapisystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B42BDF-F135-4A19-9538-F00DD08C7812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB908C5FFD8772A2A8376708C8270D888CD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA135683-F802-45AE-86B1-634C1D0F8C97}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Fodterapisystemer">'Opdateret d. 09-10-2026'!$A$1:$I$17</definedName>
+    <definedName name="Fodterapisystemer">'Opdateret d. 23-10-2026'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
